--- a/data/trans_orig/P1413-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2007</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>85990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122247</t>
+          <t>122450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92856</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128068</t>
+          <t>128194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189413</t>
+          <t>188247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241830</t>
+          <t>240494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571765</t>
+          <t>571562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>608365</t>
+          <t>608022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>560283</t>
+          <t>560157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>595495</t>
+          <t>595721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1140533</t>
+          <t>1141869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1192950</t>
+          <t>1194116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110213</t>
+          <t>108925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151953</t>
+          <t>153059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166036</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216980</t>
+          <t>218176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288694</t>
+          <t>288415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354914</t>
+          <t>355847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>809847</t>
+          <t>808741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>851587</t>
+          <t>852875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>751413</t>
+          <t>750217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>802357</t>
+          <t>801742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1575279</t>
+          <t>1574346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1641499</t>
+          <t>1641778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115241</t>
+          <t>118058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>159138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158889</t>
+          <t>158019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202989</t>
+          <t>204260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288975</t>
+          <t>288433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348035</t>
+          <t>349804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520716</t>
+          <t>519371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>563268</t>
+          <t>560451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>480852</t>
+          <t>479581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524952</t>
+          <t>525822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1014315</t>
+          <t>1012546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073375</t>
+          <t>1073917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140145</t>
+          <t>139647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185680</t>
+          <t>182415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145264</t>
+          <t>145742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191490</t>
+          <t>193549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>297131</t>
+          <t>294392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360836</t>
+          <t>361394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756542</t>
+          <t>759807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802077</t>
+          <t>802575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>847122</t>
+          <t>845063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>893348</t>
+          <t>892870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619998</t>
+          <t>1619440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1683703</t>
+          <t>1686442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>485131</t>
+          <t>491205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>571871</t>
+          <t>571470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>604265</t>
+          <t>602194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>696767</t>
+          <t>692257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1109635</t>
+          <t>1123590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1242998</t>
+          <t>1242838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2704672</t>
+          <t>2705073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2791412</t>
+          <t>2785338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2682430</t>
+          <t>2686940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2774932</t>
+          <t>2777003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5412743</t>
+          <t>5412903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5546106</t>
+          <t>5532151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2012</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63410</t>
+          <t>63799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96074</t>
+          <t>98799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124516</t>
+          <t>125701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169817</t>
+          <t>169984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197366</t>
+          <t>198922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254636</t>
+          <t>254135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>607395</t>
+          <t>604670</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>640059</t>
+          <t>639670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>527233</t>
+          <t>527066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>572534</t>
+          <t>571349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1145883</t>
+          <t>1146384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1203153</t>
+          <t>1201597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87374</t>
+          <t>88000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127157</t>
+          <t>127501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156092</t>
+          <t>158866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210391</t>
+          <t>206033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>256871</t>
+          <t>255264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321017</t>
+          <t>320881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890790</t>
+          <t>890446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>930573</t>
+          <t>929947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>818582</t>
+          <t>822940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>872881</t>
+          <t>870107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1725904</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1790050</t>
+          <t>1791657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65150</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99024</t>
+          <t>95377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140190</t>
+          <t>137901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144387</t>
+          <t>141786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>190798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692473</t>
+          <t>692144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>721913</t>
+          <t>722240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636984</t>
+          <t>639273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678150</t>
+          <t>681797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1341539</t>
+          <t>1343999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1390410</t>
+          <t>1393011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58781</t>
+          <t>58988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93563</t>
+          <t>94580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177178</t>
+          <t>177060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228092</t>
+          <t>229934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245080</t>
+          <t>246917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>309435</t>
+          <t>309628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854176</t>
+          <t>853159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>888958</t>
+          <t>888751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>823809</t>
+          <t>821967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>874723</t>
+          <t>874841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1690205</t>
+          <t>1690012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1754560</t>
+          <t>1752723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>278211</t>
+          <t>278887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>345079</t>
+          <t>345582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>599713</t>
+          <t>602211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>696141</t>
+          <t>694407</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>899865</t>
+          <t>896548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1016775</t>
+          <t>1013551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3081700</t>
+          <t>3081197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3148568</t>
+          <t>3147892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2858957</t>
+          <t>2860691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2955385</t>
+          <t>2952887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5965102</t>
+          <t>5968326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6082012</t>
+          <t>6085329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2016</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47587</t>
+          <t>48569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77528</t>
+          <t>78910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82499</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118939</t>
+          <t>120097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139774</t>
+          <t>137995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186383</t>
+          <t>185174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597272</t>
+          <t>595890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>627213</t>
+          <t>626231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>553900</t>
+          <t>552742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>590340</t>
+          <t>590776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1161256</t>
+          <t>1162465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1207865</t>
+          <t>1209644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64443</t>
+          <t>63722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100522</t>
+          <t>98671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121331</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168229</t>
+          <t>163429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195165</t>
+          <t>194060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253653</t>
+          <t>253334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>921909</t>
+          <t>923760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>957988</t>
+          <t>958709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>874684</t>
+          <t>879484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921582</t>
+          <t>925589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1811691</t>
+          <t>1812010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870179</t>
+          <t>1871284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37276</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65603</t>
+          <t>64915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67524</t>
+          <t>67400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101477</t>
+          <t>102462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111084</t>
+          <t>111684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155809</t>
+          <t>158253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>693949</t>
+          <t>694637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>722276</t>
+          <t>721264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>683534</t>
+          <t>682549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>717487</t>
+          <t>717611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1388754</t>
+          <t>1386310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1433479</t>
+          <t>1432879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68903</t>
+          <t>69299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105744</t>
+          <t>105258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144148</t>
+          <t>142814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193129</t>
+          <t>191212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224797</t>
+          <t>223973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>287097</t>
+          <t>288863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831823</t>
+          <t>832309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868664</t>
+          <t>868268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>850650</t>
+          <t>852567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>899631</t>
+          <t>900965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1694249</t>
+          <t>1692483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1756549</t>
+          <t>1757373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>245425</t>
+          <t>246051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>315170</t>
+          <t>310896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>444603</t>
+          <t>453078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>535404</t>
+          <t>541806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>715865</t>
+          <t>716938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>826964</t>
+          <t>823410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3079180</t>
+          <t>3083454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3148925</t>
+          <t>3148299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3009138</t>
+          <t>3002736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3099939</t>
+          <t>3091464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6111928</t>
+          <t>6115482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6223027</t>
+          <t>6221954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2023</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107482</t>
+          <t>107046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146396</t>
+          <t>145040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191905</t>
+          <t>191876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229138</t>
+          <t>228638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310927</t>
+          <t>310880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365110</t>
+          <t>363293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489045</t>
+          <t>490401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>527959</t>
+          <t>528395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446232</t>
+          <t>446732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>483465</t>
+          <t>483494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>945701</t>
+          <t>947518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>999884</t>
+          <t>999931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81393</t>
+          <t>79315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209653</t>
+          <t>210167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>287056</t>
+          <t>285037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>332789</t>
+          <t>333014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319053</t>
+          <t>304249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>543254</t>
+          <t>542406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979837</t>
+          <t>979323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1108097</t>
+          <t>1110175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>624003</t>
+          <t>623778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>669736</t>
+          <t>671755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1603028</t>
+          <t>1603876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1827229</t>
+          <t>1842033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118788</t>
+          <t>117831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163996</t>
+          <t>161923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278849</t>
+          <t>281734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>671105</t>
+          <t>714036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>405283</t>
+          <t>409599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>974985</t>
+          <t>916111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538969</t>
+          <t>541042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584177</t>
+          <t>585134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262101</t>
+          <t>219170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654357</t>
+          <t>651472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>661186</t>
+          <t>720060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1230888</t>
+          <t>1226572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155522</t>
+          <t>155198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>203894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228180</t>
+          <t>229960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>311252</t>
+          <t>313405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>404075</t>
+          <t>402461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>496140</t>
+          <t>495902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>722421</t>
+          <t>722177</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>770549</t>
+          <t>770873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>780662</t>
+          <t>778509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863734</t>
+          <t>861954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1521846</t>
+          <t>1522084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1613911</t>
+          <t>1615525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>477330</t>
+          <t>465913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>669457</t>
+          <t>668553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1071397</t>
+          <t>1069708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1691433</t>
+          <t>1662016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1638912</t>
+          <t>1629138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2431812</t>
+          <t>2479075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2784511</t>
+          <t>2785415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2976638</t>
+          <t>2988055</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1965849</t>
+          <t>1995266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2585885</t>
+          <t>2587574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4679438</t>
+          <t>4632175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5472338</t>
+          <t>5482112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1413-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85990</t>
+          <t>83953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122450</t>
+          <t>124214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92630</t>
+          <t>92926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128194</t>
+          <t>129659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188247</t>
+          <t>186921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>240494</t>
+          <t>241178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571562</t>
+          <t>569798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>608022</t>
+          <t>610059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>560157</t>
+          <t>558692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>595721</t>
+          <t>595425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1141869</t>
+          <t>1141185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1194116</t>
+          <t>1195442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108925</t>
+          <t>108845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153059</t>
+          <t>151754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166651</t>
+          <t>167717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218176</t>
+          <t>217290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288415</t>
+          <t>288783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355847</t>
+          <t>355141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>808741</t>
+          <t>810046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>852875</t>
+          <t>852955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>750217</t>
+          <t>751103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>801742</t>
+          <t>800676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1574346</t>
+          <t>1575052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1641778</t>
+          <t>1641410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118058</t>
+          <t>117610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159138</t>
+          <t>160785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158019</t>
+          <t>157480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>204260</t>
+          <t>201228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288433</t>
+          <t>288866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349804</t>
+          <t>351803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519371</t>
+          <t>517724</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560451</t>
+          <t>560899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479581</t>
+          <t>482613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525822</t>
+          <t>526361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1012546</t>
+          <t>1010547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073917</t>
+          <t>1073484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139647</t>
+          <t>139967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182415</t>
+          <t>183276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145742</t>
+          <t>146620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193549</t>
+          <t>191589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294392</t>
+          <t>295742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361394</t>
+          <t>361111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>759807</t>
+          <t>758946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802575</t>
+          <t>802255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>845063</t>
+          <t>847023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>892870</t>
+          <t>891992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619440</t>
+          <t>1619723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1686442</t>
+          <t>1685092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>491205</t>
+          <t>491274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>571470</t>
+          <t>578124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602194</t>
+          <t>601826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>692257</t>
+          <t>696772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1123590</t>
+          <t>1116665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1242838</t>
+          <t>1239970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2705073</t>
+          <t>2698419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2785338</t>
+          <t>2785269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2686940</t>
+          <t>2682425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2777003</t>
+          <t>2777371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5412903</t>
+          <t>5415771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5532151</t>
+          <t>5539076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63799</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98799</t>
+          <t>98720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125701</t>
+          <t>123105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169984</t>
+          <t>168373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198922</t>
+          <t>197217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254135</t>
+          <t>252622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>604670</t>
+          <t>604749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>639670</t>
+          <t>641928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>527066</t>
+          <t>528677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571349</t>
+          <t>573945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1146384</t>
+          <t>1147897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1201597</t>
+          <t>1203302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88000</t>
+          <t>86933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127501</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158866</t>
+          <t>154820</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206033</t>
+          <t>208334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255264</t>
+          <t>254177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320881</t>
+          <t>319744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890446</t>
+          <t>888836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>929947</t>
+          <t>931014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>822940</t>
+          <t>820639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>870107</t>
+          <t>874153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1727177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1791657</t>
+          <t>1792744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35383</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65479</t>
+          <t>64628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95377</t>
+          <t>99065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>138570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141786</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190798</t>
+          <t>192228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692144</t>
+          <t>692995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>722240</t>
+          <t>721221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639273</t>
+          <t>638604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681797</t>
+          <t>678109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1343999</t>
+          <t>1342569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1393011</t>
+          <t>1391805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58988</t>
+          <t>60235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94580</t>
+          <t>95215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177060</t>
+          <t>176817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229934</t>
+          <t>228279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246917</t>
+          <t>246863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>309628</t>
+          <t>310971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853159</t>
+          <t>852524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>888751</t>
+          <t>887504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>821967</t>
+          <t>823622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>874841</t>
+          <t>875084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1690012</t>
+          <t>1688669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1752723</t>
+          <t>1752777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>278887</t>
+          <t>272492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>345582</t>
+          <t>346774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602211</t>
+          <t>599804</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694407</t>
+          <t>695235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>896548</t>
+          <t>895592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1013551</t>
+          <t>1019284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3081197</t>
+          <t>3080005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3147892</t>
+          <t>3154287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2860691</t>
+          <t>2859863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2952887</t>
+          <t>2955294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5968326</t>
+          <t>5962593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6085329</t>
+          <t>6086285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48569</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78910</t>
+          <t>75581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>81040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120097</t>
+          <t>118592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137995</t>
+          <t>139179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185174</t>
+          <t>187021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>595890</t>
+          <t>599219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>626231</t>
+          <t>627542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>552742</t>
+          <t>554247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>590776</t>
+          <t>591799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1162465</t>
+          <t>1160618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1209644</t>
+          <t>1208460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63722</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98671</t>
+          <t>100093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117324</t>
+          <t>117805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163429</t>
+          <t>164965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194060</t>
+          <t>193187</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253334</t>
+          <t>252334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>923760</t>
+          <t>922338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>958709</t>
+          <t>958610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>879484</t>
+          <t>877948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925589</t>
+          <t>925108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1812010</t>
+          <t>1813010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1871284</t>
+          <t>1872157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38288</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64915</t>
+          <t>63320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67400</t>
+          <t>66318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102462</t>
+          <t>103128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111684</t>
+          <t>113838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158253</t>
+          <t>158913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>694637</t>
+          <t>696232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>721264</t>
+          <t>723997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682549</t>
+          <t>681883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>717611</t>
+          <t>718693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1386310</t>
+          <t>1385650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1432879</t>
+          <t>1430725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69299</t>
+          <t>70319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105258</t>
+          <t>106807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142814</t>
+          <t>143060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191212</t>
+          <t>194188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223973</t>
+          <t>224792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288863</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>832309</t>
+          <t>830760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868268</t>
+          <t>867248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>852567</t>
+          <t>849591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>900965</t>
+          <t>900719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1692483</t>
+          <t>1696491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1757373</t>
+          <t>1756554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246051</t>
+          <t>245974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>310896</t>
+          <t>309842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>453078</t>
+          <t>451864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>541806</t>
+          <t>539195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>716938</t>
+          <t>721383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>823410</t>
+          <t>829037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3083454</t>
+          <t>3084508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3148299</t>
+          <t>3148376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3002736</t>
+          <t>3005347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3091464</t>
+          <t>3092678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6115482</t>
+          <t>6109855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6221954</t>
+          <t>6217509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>126378</t>
+          <t>135390</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107046</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145040</t>
+          <t>154146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>209972</t>
+          <t>227620</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191876</t>
+          <t>206564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228638</t>
+          <t>247307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>336350</t>
+          <t>363011</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310880</t>
+          <t>337892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>363293</t>
+          <t>391289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>509063</t>
+          <t>555320</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490401</t>
+          <t>536564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>528395</t>
+          <t>576817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>465398</t>
+          <t>505102</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446732</t>
+          <t>485415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>483494</t>
+          <t>526158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>974461</t>
+          <t>1060420</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>947518</t>
+          <t>1032142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>999931</t>
+          <t>1085539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>158785</t>
+          <t>174790</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79315</t>
+          <t>149087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>210167</t>
+          <t>198984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>308890</t>
+          <t>343345</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285037</t>
+          <t>315187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>333014</t>
+          <t>368985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>467675</t>
+          <t>518134</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>304249</t>
+          <t>481479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542406</t>
+          <t>556618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1030705</t>
+          <t>870510</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979323</t>
+          <t>846316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1110175</t>
+          <t>896213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>647902</t>
+          <t>726151</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>623778</t>
+          <t>700511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>671755</t>
+          <t>754309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1678607</t>
+          <t>1596662</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1603876</t>
+          <t>1558178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1842033</t>
+          <t>1633317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1189490</t>
+          <t>1045300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1189490</t>
+          <t>1045300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1189490</t>
+          <t>1045300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956792</t>
+          <t>1069496</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956792</t>
+          <t>1069496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956792</t>
+          <t>1069496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2146282</t>
+          <t>2114796</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2146282</t>
+          <t>2114796</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2146282</t>
+          <t>2114796</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>160737</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117831</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161923</t>
+          <t>186708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>434208</t>
+          <t>265568</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>281734</t>
+          <t>241977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>292637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>574358</t>
+          <t>426305</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>409599</t>
+          <t>393827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>916111</t>
+          <t>462486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>562816</t>
+          <t>640480</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541042</t>
+          <t>614509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585134</t>
+          <t>663990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>498998</t>
+          <t>546008</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219170</t>
+          <t>518939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651472</t>
+          <t>569599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1061813</t>
+          <t>1186488</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>720060</t>
+          <t>1150307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1226572</t>
+          <t>1218966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636171</t>
+          <t>1612793</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636171</t>
+          <t>1612793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636171</t>
+          <t>1612793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>176748</t>
+          <t>183360</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155198</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203894</t>
+          <t>206683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>280594</t>
+          <t>305402</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229960</t>
+          <t>281831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>313405</t>
+          <t>329958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>457342</t>
+          <t>488762</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>402461</t>
+          <t>457295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495902</t>
+          <t>530188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>749323</t>
+          <t>805811</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>722177</t>
+          <t>782488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>770873</t>
+          <t>827920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>811320</t>
+          <t>812232</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>778509</t>
+          <t>787676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>861954</t>
+          <t>835803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1560644</t>
+          <t>1618043</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1522084</t>
+          <t>1576617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1615525</t>
+          <t>1649510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926071</t>
+          <t>989171</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926071</t>
+          <t>989171</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926071</t>
+          <t>989171</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017986</t>
+          <t>2106805</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017986</t>
+          <t>2106805</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017986</t>
+          <t>2106805</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>602060</t>
+          <t>654276</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>465913</t>
+          <t>607107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>668553</t>
+          <t>705157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1233663</t>
+          <t>1141936</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1069708</t>
+          <t>1093870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1662016</t>
+          <t>1190892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1835724</t>
+          <t>1796212</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1629138</t>
+          <t>1731327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2479075</t>
+          <t>1860958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2851908</t>
+          <t>2872122</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2785415</t>
+          <t>2821241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2988055</t>
+          <t>2919291</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2423619</t>
+          <t>2589492</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1995266</t>
+          <t>2540536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2587574</t>
+          <t>2637558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5275526</t>
+          <t>5461614</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4632175</t>
+          <t>5396868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5482112</t>
+          <t>5526499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
